--- a/R/R_Output.xlsx
+++ b/R/R_Output.xlsx
@@ -1,96 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Reserving Project\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{726B72C9-5667-4D97-9DF8-2A6E42972B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="R" sheetId="1" r:id="rId1"/>
+    <sheet name="R" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t>AccidentYear</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>Dev.To.Date</t>
-  </si>
-  <si>
-    <t>Ultimate</t>
-  </si>
-  <si>
-    <t>IBNR</t>
-  </si>
-  <si>
-    <t>Mack.S.E</t>
-  </si>
-  <si>
-    <t>CV(IBNR)</t>
-  </si>
-  <si>
-    <t>1998</t>
-  </si>
-  <si>
-    <t>1999</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
+    <t xml:space="preserve">AccidentYear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev.To.Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBNR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack.S.E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV(IBNR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -126,15 +106,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -416,17 +387,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,238 +414,238 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>58988</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>58988</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="e">
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>59960</v>
       </c>
-      <c r="C3">
-        <v>1.0003390520105799</v>
-      </c>
-      <c r="D3">
+      <c r="C3" t="n">
+        <v>1.00033905201058</v>
+      </c>
+      <c r="D3" t="n">
         <v>59939.6773318872</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>-20.3226681128072</v>
       </c>
-      <c r="F3">
-        <v>91.603274077280503</v>
-      </c>
-      <c r="G3">
-        <v>-4.5074432928200503</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F3" t="n">
+        <v>91.6032740772805</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-4.50744329282005</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>53788</v>
       </c>
-      <c r="C4">
-        <v>1.0029877205717299</v>
-      </c>
-      <c r="D4">
-        <v>53627.775192840098</v>
-      </c>
-      <c r="E4">
+      <c r="C4" t="n">
+        <v>1.00298772057173</v>
+      </c>
+      <c r="D4" t="n">
+        <v>53627.7751928401</v>
+      </c>
+      <c r="E4" t="n">
         <v>-160.224807159866</v>
       </c>
-      <c r="F4">
-        <v>280.34035559494998</v>
-      </c>
-      <c r="G4">
+      <c r="F4" t="n">
+        <v>280.34035559495</v>
+      </c>
+      <c r="G4" t="n">
         <v>-1.74966885942473</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>49962</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1.00404824921526</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>49760.5568647213</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>-201.443135278678</v>
       </c>
-      <c r="F5">
-        <v>275.85549830231099</v>
-      </c>
-      <c r="G5">
+      <c r="F5" t="n">
+        <v>275.855498302311</v>
+      </c>
+      <c r="G5" t="n">
         <v>-1.36939637044812</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>50306</v>
       </c>
-      <c r="C6">
-        <v>1.0043856068360899</v>
-      </c>
-      <c r="D6">
-        <v>50086.341000513297</v>
-      </c>
-      <c r="E6">
-        <v>-219.65899948674601</v>
-      </c>
-      <c r="F6">
-        <v>311.73257251736999</v>
-      </c>
-      <c r="G6">
-        <v>-1.4191659492475199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C6" t="n">
+        <v>1.00438560683609</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50086.3410005133</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-219.658999486746</v>
+      </c>
+      <c r="F6" t="n">
+        <v>311.73257251737</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.41916594924752</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>44429</v>
       </c>
-      <c r="C7">
-        <v>1.0080970285567701</v>
-      </c>
-      <c r="D7">
-        <v>44072.146570659301</v>
-      </c>
-      <c r="E7">
-        <v>-356.85342934066301</v>
-      </c>
-      <c r="F7">
-        <v>399.60516975260998</v>
-      </c>
-      <c r="G7">
+      <c r="C7" t="n">
+        <v>1.00809702855677</v>
+      </c>
+      <c r="D7" t="n">
+        <v>44072.1465706593</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-356.853429340663</v>
+      </c>
+      <c r="F7" t="n">
+        <v>399.60516975261</v>
+      </c>
+      <c r="G7" t="n">
         <v>-1.11980196040413</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>38017</v>
       </c>
-      <c r="C8">
-        <v>1.0071301260008301</v>
-      </c>
-      <c r="D8">
-        <v>37747.853051482103</v>
-      </c>
-      <c r="E8">
-        <v>-269.14694851791899</v>
-      </c>
-      <c r="F8">
-        <v>607.36351436841403</v>
-      </c>
-      <c r="G8">
-        <v>-2.2566241888043499</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" t="n">
+        <v>1.00713012600083</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37747.8530514821</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-269.146948517919</v>
+      </c>
+      <c r="F8" t="n">
+        <v>607.363514368414</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.25662418880435</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>33511</v>
       </c>
-      <c r="C9">
-        <v>1.0105968750638401</v>
-      </c>
-      <c r="D9">
+      <c r="C9" t="n">
+        <v>1.01059687506384</v>
+      </c>
+      <c r="D9" t="n">
         <v>33159.611737255</v>
       </c>
-      <c r="E9">
-        <v>-351.38826274501503</v>
-      </c>
-      <c r="F9">
-        <v>801.31761809939701</v>
-      </c>
-      <c r="G9">
-        <v>-2.2804336486357699</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" t="n">
+        <v>-351.388262745015</v>
+      </c>
+      <c r="F9" t="n">
+        <v>801.317618099397</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.28043364863577</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>30432</v>
       </c>
-      <c r="C10">
-        <v>1.0273452026594201</v>
-      </c>
-      <c r="D10">
-        <v>29621.980928340901</v>
-      </c>
-      <c r="E10">
-        <v>-810.01907165909904</v>
-      </c>
-      <c r="F10">
+      <c r="C10" t="n">
+        <v>1.02734520265942</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29621.9809283409</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-810.019071659099</v>
+      </c>
+      <c r="F10" t="n">
         <v>1002.90106395399</v>
       </c>
-      <c r="G10">
-        <v>-1.2381203098092799</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" t="n">
+        <v>-1.23812030980928</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>28721</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1.07497304970679</v>
       </c>
-      <c r="D11">
-        <v>26717.879120629201</v>
-      </c>
-      <c r="E11">
-        <v>-2003.1208793708199</v>
-      </c>
-      <c r="F11">
-        <v>1671.4229874339801</v>
-      </c>
-      <c r="G11">
-        <v>-0.83440944810029405</v>
+      <c r="D11" t="n">
+        <v>26717.8791206292</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-2003.12087937082</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671.42298743398</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.834409448100294</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>